--- a/MAJEntreesCDA/ig/StructureDefinition-fr-cda-evenement.xlsx
+++ b/MAJEntreesCDA/ig/StructureDefinition-fr-cda-evenement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:07+00:00</t>
+    <t>2026-04-20T13:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5251,7 +5251,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>168</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>74</v>
@@ -5571,7 +5571,7 @@
         <v>62</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>75</v>
@@ -5674,7 +5674,7 @@
         <v>181</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>75</v>
@@ -5983,7 +5983,7 @@
         <v>193</v>
       </c>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>75</v>
